--- a/public/templates/template-import-tarif-ranap.xlsx
+++ b/public/templates/template-import-tarif-ranap.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\smc-internal-app\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759F1A50-5361-4CE2-BF68-4889DC34F608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0535C6B2-116C-413C-97BF-E21A2E3A5EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C8077956-CB79-47B0-A3DD-FE3F8C4941F0}"/>
   </bookViews>
@@ -27,61 +27,61 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
-    <t>kd_jenis_prw</t>
-  </si>
-  <si>
-    <t>nm_perawatan</t>
-  </si>
-  <si>
-    <t>kd_kategori</t>
-  </si>
-  <si>
-    <t>material</t>
-  </si>
-  <si>
-    <t>bhp</t>
-  </si>
-  <si>
-    <t>tarif_tindakandr</t>
-  </si>
-  <si>
-    <t>tarif_tindakanpr</t>
-  </si>
-  <si>
-    <t>kso</t>
-  </si>
-  <si>
-    <t>menejemen</t>
-  </si>
-  <si>
-    <t>total_byrdr</t>
-  </si>
-  <si>
-    <t>total_byrpr</t>
-  </si>
-  <si>
-    <t>kd_pj</t>
-  </si>
-  <si>
-    <t>kd_bangsal</t>
-  </si>
-  <si>
-    <t>kelas</t>
-  </si>
-  <si>
-    <t>ADM_RI-00001</t>
-  </si>
-  <si>
-    <t>AKTE KELAHIRAN</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t>Kelas VVIP</t>
-  </si>
-  <si>
-    <t>total_byrdrpr</t>
+    <t>Kode Tindakan</t>
+  </si>
+  <si>
+    <t>Kategori</t>
+  </si>
+  <si>
+    <t>Jasa Sarana</t>
+  </si>
+  <si>
+    <t>BHP/Paket Obat</t>
+  </si>
+  <si>
+    <t>Jasa Medis Dr</t>
+  </si>
+  <si>
+    <t>KSO</t>
+  </si>
+  <si>
+    <t>Menejemen</t>
+  </si>
+  <si>
+    <t>Jenis Bayar</t>
+  </si>
+  <si>
+    <t>Kelas</t>
+  </si>
+  <si>
+    <t>ANAK_RI-A00037</t>
+  </si>
+  <si>
+    <t>ECHOCARDIOGRAFI ANAK 1</t>
+  </si>
+  <si>
+    <t>Dokter Spesialis</t>
+  </si>
+  <si>
+    <t>Jasa Medis Pr</t>
+  </si>
+  <si>
+    <t>Total Biaya Dr</t>
+  </si>
+  <si>
+    <t>Total Biaya Pr</t>
+  </si>
+  <si>
+    <t>Total Biaya Dr &amp; Pr</t>
+  </si>
+  <si>
+    <t>Kamar</t>
+  </si>
+  <si>
+    <t>Nama Tnd/Prw/Tagihan</t>
   </si>
 </sst>
 </file>
@@ -119,9 +119,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -439,87 +437,88 @@
   <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="5.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="N1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1">
-        <v>100000</v>
+        <v>79660</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
       </c>
       <c r="F2" s="1">
-        <v>0</v>
+        <v>716940</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -531,7 +530,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="1">
-        <v>100000</v>
+        <v>796600</v>
       </c>
       <c r="K2" s="1">
         <v>0</v>
@@ -540,13 +539,13 @@
         <v>0</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
